--- a/output/pdf_financials_xlsx/TECT.xlsx
+++ b/output/pdf_financials_xlsx/TECT.xlsx
@@ -3051,22 +3051,22 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.294524</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.079699</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.799782</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>7.277929</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>8.692862999999999</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>15.265243</v>
       </c>
     </row>
     <row r="93">
@@ -4941,7 +4941,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -6212,7 +6216,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TECT.xlsx
+++ b/output/pdf_financials_xlsx/TECT.xlsx
@@ -741,13 +741,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.031777</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.027346</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.196929</v>
       </c>
     </row>
     <row r="13">
@@ -1189,13 +1189,13 @@
         <v>-4.006282</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-9.599008</v>
+        <v>-9.630784999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-5.090774</v>
+        <v>-5.11812</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-23.097836</v>
+        <v>-23.294765</v>
       </c>
     </row>
     <row r="28">
@@ -1245,13 +1245,13 @@
         <v>-3.9692</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-9.584272</v>
+        <v>-9.616049</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.08712</v>
+        <v>-5.114466</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-23.047542</v>
+        <v>-23.244471</v>
       </c>
     </row>
     <row r="30">
@@ -1380,16 +1380,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.07934</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.791241</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.074068</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.552145</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>2.38131</v>
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.07934</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.791241</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.074068</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.552145</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>2.38131</v>
@@ -1772,16 +1772,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.173888</v>
+        <v>0.09454799999999999</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.98864</v>
+        <v>0.197399</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.139216</v>
+        <v>0.065148</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.757461</v>
+        <v>0.205316</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.33418</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.023491</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -3958,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.023491</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -5127,7 +5127,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
@@ -12498,7 +12498,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -13492,7 +13496,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -13857,7 +13861,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -13912,7 +13916,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -14675,7 +14679,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -14979,7 +14983,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">

--- a/output/pdf_financials_xlsx/TECT.xlsx
+++ b/output/pdf_financials_xlsx/TECT.xlsx
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.00343</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -8873,7 +8873,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TECT.xlsx
+++ b/output/pdf_financials_xlsx/TECT.xlsx
@@ -3550,10 +3550,10 @@
         <v>0</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.011197</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.012058</v>
       </c>
     </row>
     <row r="111">
@@ -6373,7 +6373,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -8367,7 +8371,11 @@
           <t>Units issued in private placement 25,472,600 8,447,819 4,288,481</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
